--- a/release/v2026.3.0/ValueSet-mii-qst-pro-eortc-qlq-c30_mii-qst-pro-eortc-qlq-c30.xlsx
+++ b/release/v2026.3.0/ValueSet-mii-qst-pro-eortc-qlq-c30_mii-qst-pro-eortc-qlq-c30.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.2.0</t>
+    <t>2026.3.0</t>
   </si>
   <si>
     <t>Name</t>
